--- a/artfynd/S 2213-2022 artfynd.xlsx
+++ b/artfynd/S 2213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128487361</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121163986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118772404</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164077</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164538</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164539</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907535</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164162</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907516</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907517</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93040859</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164628</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164707</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121266939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907520</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907343</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2897,6 +3002,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014957</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014964</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3115,6 +3230,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116650908</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3217,6 +3337,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164540</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3319,6 +3444,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164306</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3421,6 +3551,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164308</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3523,6 +3658,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164309</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3625,6 +3765,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121163981</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3727,6 +3872,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164846</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3829,6 +3979,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164621</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3931,6 +4086,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121164632</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4036,6 +4196,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92935393</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4141,6 +4306,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92899455</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4260,6 +4430,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95871008</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4365,6 +4540,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92515651</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4467,6 +4647,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907494</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4573,6 +4758,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907340</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4675,6 +4865,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907374</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4799,6 +4994,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93582302</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4916,6 +5116,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115080321</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5022,6 +5227,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87907528</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5128,6 +5338,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735603</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5229,6 +5444,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014832</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5331,6 +5551,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014912</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5432,6 +5657,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014941</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5563,6 +5793,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97686237</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5665,6 +5900,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121163985</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5772,6 +6012,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014828</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5871,6 +6116,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014834</t>
         </is>
       </c>
     </row>
@@ -5985,6 +6235,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014836</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6091,6 +6346,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014837</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6197,6 +6457,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014839</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6303,6 +6568,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014840</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6413,6 +6683,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014986</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6523,6 +6798,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014987</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6620,6 +6900,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014911</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6722,6 +7007,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014913</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6824,8 +7114,73 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94014916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>